--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -502,12 +502,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>الاحكام الصادرة في القضية - 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -573,21 +573,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -613,17 +613,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -640,26 +644,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مرفقات المدعي بموقع ناجز في الدعوى رقم 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -676,26 +684,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -712,26 +724,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,26 +764,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -784,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -793,17 +813,21 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -820,26 +844,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -856,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -865,17 +893,21 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -892,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -901,17 +933,21 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -928,26 +964,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>صحيفة دعوى</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4530828230</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -964,26 +1004,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4530828230</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1000,26 +1044,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1036,26 +1084,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1072,26 +1124,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1108,26 +1164,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1144,26 +1204,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4431025114؛ 4530241622</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1180,26 +1244,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1216,26 +1280,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1252,26 +1320,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1288,26 +1360,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1324,26 +1400,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1360,26 +1440,30 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>محضر</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1404,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1496,17 +1580,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 137631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>الاحكام الصادرة في القضية - 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1558,17 +1642,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 1445 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1620,17 +1704,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1682,17 +1766,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 331,882,138، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1739,22 +1823,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>مبالغ: 1,400,000.00، 250,000,000، 172,613,467</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مرفقات المدعي بموقع ناجز في الدعوى رقم 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1801,22 +1885,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1863,22 +1947,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 137631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1925,22 +2009,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1992,17 +2076,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2049,22 +2133,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2116,17 +2200,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2178,17 +2262,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>مبالغ: 450</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2235,22 +2319,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 500.000، 450000</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>مستندات قضية 42824717</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2297,22 +2381,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2359,22 +2443,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2421,22 +2505,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 120,000,000، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2483,22 +2567,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2545,22 +2629,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2607,22 +2691,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>مبالغ: 120,000,000، 110,672,379، 331,882,138 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2669,22 +2753,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>مبالغ: 331,882,138، 368,757,931، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2736,17 +2820,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2798,17 +2882,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 450.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2860,17 +2944,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2922,17 +3006,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>مبالغ: 335,184,145، 368.757.931، 372.426.828 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2984,17 +3068,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3046,17 +3130,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>محاضر ضبط الجلسات للدعوى 42824717</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3108,50 +3192,4266 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | مبالغ: 36877936، 79929906، 150,000 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>قضايا: 42824717</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>مبالغ: 450</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>مبالغ: 1,400,000.00، 250,000,000، 172,613,467</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>مبالغ: 1,037259,019، 172,613,467، 11,679,151</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>مبالغ: 17,698,860,51، 36,816,648,91، 18,408,324,46</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>مبالغ: 100000000، 46,000، 1000</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>مبالغ: 500,000، 500.000، 1000</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (2)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>مبالغ: 500.000، 500,000، 450000</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>دليل/مستند</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>تفاصيل الشكوى</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>إحالة قضائية</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>مبالغ: 372.426.828، 368.757.931، 335,184,145 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>صفحة 3 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>مستندات قضية 42824717</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>مبالغ: 500.000، 500,000، 1000</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>مبالغ: 500,000، 500.000، 450,000</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>A080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>A081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>A082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>مبالغ: 685، 198</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ملف المسحوبات (Excel)</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>A084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>A085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>A087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>A088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>A089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>A090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>A091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>A092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>A093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>A094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>A095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>صفحة 1 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,12 +577,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,11 +853,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,12 +1084,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,12 +1164,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1204,7 +1204,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1213,21 +1213,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1244,26 +1244,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1280,20 +1284,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1303,7 +1307,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1320,20 +1324,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1343,7 +1347,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1360,30 +1364,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1400,12 +1404,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1413,17 +1417,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1440,12 +1440,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>مذكرة قضائية</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 137631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331882.138، 137631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 20,043,862 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 137631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331882.138، 137631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2567,22 +2567,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2696,17 +2696,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2753,22 +2753,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>مبالغ: 331,882,138، 368,757,931، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2939,22 +2939,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>مبالغ: 331,882,138، 368,757,931، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3316,17 +3316,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 36877936، 79929906، 150,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3745,22 +3745,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>مبالغ: 450</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3807,22 +3807,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3869,22 +3869,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>مبالغ: 1,400,000.00، 250,000,000، 172,613,467</t>
+          <t>صكوك: 4530241622 | مبالغ: 79929906، 36877936، 150,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3931,22 +3931,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>مبالغ: 1,037259,019، 172,613,467، 11,679,151</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3993,22 +3993,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>مبالغ: 17,698,860,51، 36,816,648,91، 18,408,324,46</t>
+          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4055,22 +4055,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
+          <t>مبالغ: 36.8160648.91، 17.698.860.51، 3004840892019</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4179,22 +4179,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4241,22 +4241,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4303,22 +4303,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4365,22 +4365,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4427,22 +4427,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4494,17 +4494,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 2,463,761، 4,690,483</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>مبالغ: 1,400,000.00، 217,250,000، 172,613,467</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4613,22 +4613,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 100000000، 46,000، 1000</t>
+          <t>مبالغ: 1,037259,019، 172,613,467، 14,282,008</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4675,22 +4675,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 500.000، 1000</t>
+          <t>مبالغ: 36,816,648,91، 15,242,446,10، 18,408,324,46</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4737,22 +4737,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 27651219، 96779270</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 450000</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4923,22 +4923,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5171,22 +5171,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5233,17 +5233,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>مبالغ: 372.426.828، 368.757.931، 335,184,145 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5295,22 +5295,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
+          <t>مبالغ: 2,463,761، 4,690,483</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>مبالغ: 100000000، 46,000، 1000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>مبالغ: 500.000، 500,000، 1000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5543,17 +5543,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 500.000، 450000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 1000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 500.000، 450,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5858,17 +5858,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5920,17 +5920,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5982,17 +5982,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6106,17 +6106,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 135 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 335,184,145، 368.757.931، 372.426.828 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6354,17 +6354,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6478,17 +6478,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6607,12 +6607,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6664,17 +6664,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>مبالغ: 685، 198</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ملف المسحوبات (Excel)</t>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6850,17 +6850,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 500.000، 1000</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 500.000، 450,000، 500,000</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>موجز إعادة فتح الشكوى</t>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>صورة التقديم (jpg)</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7413,45 +7413,1471 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>A096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>A097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>A098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>A099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>A101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>A102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>A103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>مبالغ: 685، 198</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ملف المسحوبات (Excel)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>A104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>A105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>A106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>A107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>A108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>A109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>A110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>A111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>A112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>A113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>A114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>A115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>A116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>A117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>A118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>مبالغ: 331,882,138، 368,757,931، 450,000 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 331,882,138، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
+          <t>مبالغ: 3700,000,000، 370,000,000، 120,000,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 2,463,761، 4,690,483</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 1,400,000.00، 217,250,000، 172,613,467</t>
+          <t>مبالغ: 1,400,000.00، 250,000,000، 172,613,467</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 1,037259,019، 172,613,467، 14,282,008</t>
+          <t>مبالغ: 1,037259,019، 172,613,467، 11,679,151</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 36,816,648,91، 15,242,446,10، 18,408,324,46</t>
+          <t>مبالغ: 18,408,324,46، 17,698,860,51، 15,242,446,10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 2,463,761، 4,690,483</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>مبالغ: 100000000، 46,000، 1000</t>
+          <t>مبالغ: 17,000، 20,000، 1000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>المسحوبات 1434 (zip)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 1000</t>
+          <t>مبالغ: 25,000، 30,000، 22,500</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>المسحوبات 1435 (zip)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5486,17 +5486,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 60,000، 26,100، 30,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>المسحوبات 1436 (zip)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 500.000، 450000</t>
+          <t>مبالغ: 13,908.10، 16,623.26، 40901050</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>المسحوبات 2015 (zip)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5605,22 +5605,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 100000000، 46,000، 1000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5672,17 +5672,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500.000، 500,000، 1000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5791,22 +5791,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 500.000، 500,000، 450000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5853,22 +5853,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5915,22 +5915,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5977,22 +5977,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 10851</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>مزرعة الوادي 1433 (zip)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 9290، 9240</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6101,22 +6101,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 19,000,500، 350.00، 01318</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+          <t>فلة الوادي 1433 (rar)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>مبالغ: 135 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>مبالغ: 335,184,145، 368.757.931، 372.426.828 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6473,22 +6473,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6602,17 +6602,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 135 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6664,17 +6664,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 368.757.931، 372.426.828، 335,184,145 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 368.757.931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6788,17 +6788,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6850,17 +6850,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 500.000، 1000</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 450,000، 500,000</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500.000، 500,000، 1000</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7346,17 +7346,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500.000، 500,000، 450,000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>مبالغ: 685، 198</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ملف المسحوبات (Excel)</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8090,17 +8090,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 198، 685</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+          <t>ملف المسحوبات (Excel)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>موجز إعادة فتح الشكوى</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>صورة التقديم (jpg)</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 5.56415</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8839,45 +8839,603 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>A119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>A120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>A121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>A122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>A123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>A124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>A125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>A126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>A127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
           <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331882.138، 137631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 331882.138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 5000000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331882.138، 137631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 331882.138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 500.000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 79929906، 36877936، 150,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 36877936، 79929906، 150,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>مبالغ: 36.8160648.91، 17.698.860.51، 3004840892019</t>
+          <t>مبالغ: 3004840892019، 36.8160648.91، 17.698.860.51</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مبالغ: 3700,000,000، 370,000,000، 120,000,000</t>
+          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>مبالغ: 2,463,761، 4,690,483</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 1,400,000.00، 250,000,000، 172,613,467</t>
+          <t>مبالغ: 1,400,000.00، 172,613,467، 250,000,000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 18,408,324,46، 17,698,860,51، 15,242,446,10</t>
+          <t>مبالغ: 36,816,648,91، 18,408,324,46، 15,242,446,10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 27651219، 96779270</t>
+          <t>صكوك: 4530241622 | مبالغ: 96779270، 27651219</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>مبالغ: 2,463,761، 4,690,483</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 25,000، 30,000، 22,500</t>
+          <t>مبالغ: 22,500، 25,000، 30,000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>مبالغ: 60,000، 26,100، 30,000</t>
+          <t>مبالغ: 60,900، 26,100، 60,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>مبالغ: 13,908.10، 16,623.26، 40901050</t>
+          <t>مبالغ: 16,623.26، 13,908.10، 40901050</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>مبالغ: 9290، 9240</t>
+          <t>مبالغ: 9240، 9290</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 372.426.828، 335,184,145 | قضايا: 42824717</t>
+          <t>مبالغ: 368.757.931، 335,184,145، 372.426.828 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
+          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 450,000</t>
+          <t>مبالغ: 500.000، 450,000، 500,000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 331882.138 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 1445 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 1,445 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 5000000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 5,000,000، 500,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 79,924,901، 331882.138 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100000000، 450,000، 500.000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 36877936، 79929906، 150,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 79,929,906، 36,877,936، 150,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 00000000000000، 137,631,929، 368,757931 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>مبالغ: 3004840892019، 36.8160648.91، 17.698.860.51</t>
+          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مبالغ: 3700,000,000، 120,000,000، 370,000,000</t>
+          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 2,463,761، 4,690,483</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 1,400,000.00، 172,613,467، 250,000,000</t>
+          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 1,037259,019، 172,613,467، 11,679,151</t>
+          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 36,816,648,91، 18,408,324,46، 15,242,446,10</t>
+          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 96779270، 27651219</t>
+          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>مبالغ: 120,000,000، 368,000,000، 450,000</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 2,463,761، 4,690,483</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>مبالغ: 17,000، 20,000، 1000</t>
+          <t>مبالغ: 20,000، 17,000، 1,000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 22,500، 25,000، 30,000</t>
+          <t>مبالغ: 36,171، 30,000، 25,000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>مبالغ: 60,900، 26,100، 60,000</t>
+          <t>مبالغ: 60,900، 60,000، 30,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>مبالغ: 16,623.26، 13,908.10، 40901050</t>
+          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>مبالغ: 100000000، 46,000، 1000</t>
+          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 1000</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 450000</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>مبالغ: 10851</t>
+          <t>مبالغ: 10,851</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>مبالغ: 9240، 9290</t>
+          <t>مبالغ: 9,290، 9,240</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>مبالغ: 19,000,500، 350.00، 01318</t>
+          <t>مبالغ: 19,000,500، 35,000، 1,318</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 335,184,145، 372.426.828 | قضايا: 42824717</t>
+          <t>مبالغ: 372,426,828، 368,757,931، 335,184,145 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>مبالغ: 368.757.931، 27,932,012، 97,762,042 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 500,000، 1000</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>مبالغ: 500.000، 450,000، 500,000</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>مبالغ: 198، 685</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ملف المسحوبات (Excel)</t>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8710,17 +8710,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 556,415</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>مبالغ: 5.56415</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>صورة تقديم الشكوى</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى</t>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+          <t>موجز إعادة فتح الشكوى</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>موجز إعادة فتح الشكوى</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+          <t>صورة التقديم (jpg)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>صورة التقديم (jpg)</t>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+          <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9374,68 +9374,6 @@
         </is>
       </c>
       <c r="L127" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>A127</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>صفحة 1 من تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4431025114</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4630548401</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,12 +1164,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1244,30 +1244,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1284,30 +1284,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1324,16 +1320,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>مذكرة قضائية</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1347,7 +1343,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1364,30 +1360,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1404,12 +1400,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1417,13 +1413,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1440,12 +1440,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 1,445 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2567,22 +2567,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2753,22 +2753,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 331,882,138، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2939,22 +2939,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 331,882,138، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3311,22 +3311,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3373,22 +3373,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3435,22 +3435,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>مبالغ: 450</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3807,22 +3807,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3869,22 +3869,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 79,929,906، 36,877,936، 150,000 | قضايا: 42824717</t>
+          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3931,22 +3931,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3993,22 +3993,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4055,22 +4055,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
+          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4122,17 +4122,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4179,22 +4179,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4246,17 +4246,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4303,22 +4303,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4365,22 +4365,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>مبالغ: 450</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4427,22 +4427,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4489,22 +4489,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>مبالغ: 20,000، 17,000، 1,000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+          <t>المسحوبات 1434 (zip)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4551,22 +4551,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
+          <t>مبالغ: 36,171، 30,000، 25,000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>المسحوبات 1435 (zip)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4613,22 +4613,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
+          <t>مبالغ: 60,900، 60,000، 30,000</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+          <t>المسحوبات 1436 (zip)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4675,22 +4675,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
+          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>المسحوبات 2015 (zip)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4923,22 +4923,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4985,22 +4985,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5047,22 +5047,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5114,17 +5114,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5233,22 +5233,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5295,22 +5295,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>مبالغ: 20,000، 17,000، 1,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>المسحوبات 1434 (zip)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 36,171، 30,000، 25,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>المسحوبات 1435 (zip)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>مبالغ: 60,900، 60,000، 30,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>المسحوبات 1436 (zip)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5543,22 +5543,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>المسحوبات 2015 (zip)</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5610,17 +5610,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5667,22 +5667,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 450,000، 1,000</t>
+          <t>مبالغ: 10,851</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>مزرعة الوادي 1433 (zip)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5853,22 +5853,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 9,290، 9,240</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5920,17 +5920,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 19,000,500، 35,000، 1,318</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+          <t>فلة الوادي 1433 (rar)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5977,22 +5977,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>مبالغ: 10,851</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1433 (zip)</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>مبالغ: 9,290، 9,240</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6101,22 +6101,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>مبالغ: 19,000,500، 35,000، 1,318</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>فلة الوادي 1433 (rar)</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6287,22 +6287,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6354,17 +6354,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 135 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6473,22 +6473,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 372,426,828، 368,757,931، 335,184,145 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6602,17 +6602,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>مبالغ: 135 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6664,17 +6664,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>مبالغ: 372,426,828، 368,757,931، 335,184,145 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6788,17 +6788,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6850,17 +6850,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6912,17 +6912,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6974,17 +6974,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7041,12 +7041,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7098,17 +7098,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7160,17 +7160,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 450,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 556,415</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صورة تقديم الشكوى</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>موجز إعادة فتح الشكوى</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>صورة التقديم (jpg)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8462,17 +8462,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8506,874 +8506,6 @@
         </is>
       </c>
       <c r="L113" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>A113</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>A114</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>A115</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>A116</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>مبالغ: 556,415</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>فلة الوادي 2015 (rar)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>A117</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>A118</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>A119</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>A120</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>صورة تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>A121</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>A122</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>موجز إعادة فتح الشكوى</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>A123</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>A124</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>صورة التقديم (jpg)</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>A125</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>A126</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>صفحة 1 من تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4431025114</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4630548401</t>
+          <t>4431025114</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2386,17 +2386,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3311,22 +3311,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3373,22 +3373,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3435,22 +3435,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>مبالغ: 450</t>
+          <t>صكوك: 4530241622 | مبالغ: 79,929,906، 36,877,936، 150,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3807,22 +3807,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3993,22 +3993,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
+          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4055,22 +4055,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4179,22 +4179,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4246,17 +4246,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4303,22 +4303,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4370,17 +4370,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4489,22 +4489,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 20,000، 17,000، 1,000</t>
+          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>المسحوبات 1434 (zip)</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 36,171، 30,000، 25,000</t>
+          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>المسحوبات 1435 (zip)</t>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4613,22 +4613,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 60,900، 60,000، 30,000</t>
+          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>المسحوبات 1436 (zip)</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4675,22 +4675,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
+          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>المسحوبات 2015 (zip)</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4737,22 +4737,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4985,22 +4985,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5052,17 +5052,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5109,22 +5109,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>مبالغ: 20,000، 17,000، 1,000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>المسحوبات 1434 (zip)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5171,22 +5171,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 36,171، 30,000، 25,000</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>المسحوبات 1435 (zip)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5233,22 +5233,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 60,900، 60,000، 30,000</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>المسحوبات 1436 (zip)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5295,22 +5295,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>المسحوبات 2015 (zip)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -902,12 +902,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4431025114</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4630548401</t>
+          <t>4431025114</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,12 +1164,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1244,30 +1244,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1284,26 +1284,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1320,16 +1324,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1360,30 +1364,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1400,12 +1404,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1413,17 +1417,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1440,12 +1440,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>شكوى</t>
+          <t>مذكرة قضائية</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1488,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 1,445 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 20,043,862 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 5,000,000، 500,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 20,043,862 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1952,17 +1952,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2567,22 +2567,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2753,22 +2753,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 331,882,138، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2939,22 +2939,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3001,22 +3001,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 331,882,138، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3316,17 +3316,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3626,17 +3626,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 79,929,906، 36,877,936، 150,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3869,22 +3869,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3931,22 +3931,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3993,22 +3993,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مبالغ: 450</t>
+          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4427,17 +4427,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4551,17 +4551,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
+          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
+          <t>مبالغ: 11,679,151، 737,500</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4675,17 +4675,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
+          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4737,17 +4737,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4923,17 +4923,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5047,22 +5047,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5109,22 +5109,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>مبالغ: 20,000، 17,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>المسحوبات 1434 (zip)</t>
+          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5171,22 +5171,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>مبالغ: 36,171، 30,000، 25,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>المسحوبات 1435 (zip)</t>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5238,17 +5238,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>مبالغ: 60,900، 60,000، 30,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>المسحوبات 1436 (zip)</t>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>المسحوبات 2015 (zip)</t>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 20,000، 17,000، 1,000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>المسحوبات 1434 (zip)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5419,22 +5419,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
+          <t>مبالغ: 36,171، 30,000، 3,325</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>المسحوبات 1435 (zip)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5486,17 +5486,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>مبالغ: 60,900، 60,000، 30,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>المسحوبات 1436 (zip)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>المسحوبات 2015 (zip)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5610,17 +5610,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 450,000، 1,000</t>
+          <t>مبالغ: 100,000,000، 1,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5667,22 +5667,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>مبالغ: 10,851</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1433 (zip)</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5853,22 +5853,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>مبالغ: 9,290، 9,240</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ح-2. المزرعة (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5920,17 +5920,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>مبالغ: 19,000,500، 35,000، 1,318</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>فلة الوادي 1433 (rar)</t>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 450,000، 1,000</t>
+          <t>مبالغ: 450,000، 1,000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7842,17 +7842,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>مبالغ: 556,415</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى</t>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>موجز إعادة فتح الشكوى</t>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>صورة التقديم (jpg)</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8462,50 +8462,670 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>مبالغ: 556,415</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>A113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>قضايا: 42824717</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>A114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>A115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>أ. المجلد الرئيسي للقضية</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>A116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>A117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>A118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>A119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>A120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>A121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>A122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
         <is>
           <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,12 +657,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -902,12 +902,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4431025114</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4630548401</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1124,12 +1124,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,12 +1164,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1244,30 +1244,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1284,30 +1284,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1324,30 +1324,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1364,7 +1360,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1373,21 +1369,17 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>4431025114؛ 4530241622</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1488,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1642,12 +1634,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 1,445 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1704,12 +1696,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>طلب النقض على صك الاستئناف الثانية</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1766,12 +1758,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1828,12 +1820,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 20,043,862 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1890,12 +1882,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 20,043,862 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1952,17 +1944,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2014,12 +2006,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2081,7 +2073,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2143,7 +2135,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2200,17 +2192,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2262,12 +2254,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2329,7 +2321,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2391,12 +2383,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2448,17 +2440,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2510,17 +2502,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2567,22 +2559,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2629,22 +2621,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2691,7 +2683,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2701,12 +2693,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2753,22 +2745,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2815,22 +2807,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2877,22 +2869,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2944,17 +2936,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3435,22 +3427,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3507,7 +3499,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3564,12 +3556,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3626,17 +3618,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3688,12 +3680,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3755,12 +3747,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3812,12 +3804,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3874,17 +3866,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3936,12 +3928,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3998,12 +3990,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4055,22 +4047,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4117,17 +4109,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 3,004,840,892,019، 36,816,064,891، 1,769,886,051</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4179,7 +4171,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4189,7 +4181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4241,7 +4233,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4251,7 +4243,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4308,12 +4300,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4370,12 +4362,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>مبالغ: 450</t>
+          <t>مبالغ: 3,700,000,000، 370,000,000، 120,000,000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4427,17 +4419,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 450</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4489,17 +4481,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>صكوك: 4530828230، 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4556,12 +4548,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4613,17 +4605,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>مبالغ: 11,679,151، 737,500</t>
+          <t>مبالغ: 250,000,000، 217,250,000، 172,613,467</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4680,17 +4672,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
+          <t>مبالغ: 11,679,151، 737,500</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4737,17 +4729,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
+          <t>مبالغ: 3,681,664,891، 3,048,489,219، 1,840,832,446</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4799,17 +4791,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>صكوك: 4530241622 | مبالغ: 96,779,270، 27,651,219</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4861,22 +4853,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4923,17 +4915,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4985,17 +4977,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,000,000، 120,000,000، 450,000</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5057,7 +5049,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5109,22 +5101,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5176,12 +5168,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 120</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5238,17 +5230,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5295,22 +5287,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>مبالغ: 20,000، 17,000، 1,000</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+          <t>المسحوبات 1434 (zip)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5362,12 +5354,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>مبالغ: 20,000، 17,000، 1,000</t>
+          <t>مبالغ: 36,171، 30,000، 3,325</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>المسحوبات 1434 (zip)</t>
+          <t>المسحوبات 1435 (zip)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5419,17 +5411,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 36,171، 30,000، 3,325</t>
+          <t>مبالغ: 60,900، 60,000، 30,000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>المسحوبات 1435 (zip)</t>
+          <t>المسحوبات 1436 (zip)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5486,12 +5478,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>مبالغ: 60,900، 60,000، 30,000</t>
+          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>المسحوبات 1436 (zip)</t>
+          <t>المسحوبات 2015 (zip)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5548,17 +5540,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
+          <t>مبالغ: 100,000,000، 1,000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>المسحوبات 2015 (zip)</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5610,12 +5602,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>مبالغ: 100,000,000، 1,000</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5672,12 +5664,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5734,17 +5726,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5791,22 +5783,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 450,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5853,7 +5845,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5863,7 +5855,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5915,22 +5907,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5987,12 +5979,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6049,7 +6041,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6111,12 +6103,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6173,12 +6165,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6225,22 +6217,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6287,17 +6279,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6354,12 +6346,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>مبالغ: 135 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6416,17 +6408,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>مبالغ: 135 | قضايا: 42824717</t>
+          <t>مبالغ: 372,426,828، 368,757,931، 335,184,145 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6478,12 +6470,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>مبالغ: 372,426,828، 368,757,931، 335,184,145 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6540,17 +6532,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6602,17 +6594,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6669,7 +6661,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6731,7 +6723,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6788,17 +6780,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6855,12 +6847,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6917,7 +6909,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6979,12 +6971,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7036,12 +7028,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7098,12 +7090,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>مبالغ: 450,000، 1,000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7160,12 +7152,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>مبالغ: 450,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7227,7 +7219,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7289,7 +7281,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7346,17 +7338,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 331,882,138، 120,000,000، 110,672,379</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7413,12 +7405,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7475,12 +7467,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7537,12 +7529,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7594,17 +7586,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7656,17 +7648,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7718,17 +7710,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7785,12 +7777,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7842,17 +7834,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 556,415</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7909,12 +7901,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7971,12 +7963,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8033,12 +8025,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8095,12 +8087,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>صورة تقديم الشكوى</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8157,12 +8149,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8214,17 +8206,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>موجز إعادة فتح الشكوى</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8276,17 +8268,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8338,17 +8330,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>صورة التقديم (jpg)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8405,7 +8397,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8462,17 +8454,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>مبالغ: 556,415</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8506,626 +8498,6 @@
         </is>
       </c>
       <c r="L113" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>A113</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>A114</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>A115</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>A116</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>صورة تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>A117</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>A118</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>موجز إعادة فتح الشكوى</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>A119</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>A120</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>صورة التقديم (jpg)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>A121</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>A122</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>صفحة 1 من تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -862,12 +862,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4431025114</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4630548401</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,12 +1084,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1204,30 +1204,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1253,21 +1253,17 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>4630548401</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1284,7 +1280,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1293,21 +1289,17 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4431025114؛ 4530241622</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1324,7 +1316,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1337,7 +1329,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1360,12 +1352,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>مذكرة قضائية</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1373,13 +1365,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1396,12 +1392,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1409,13 +1405,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 20,043,862 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2130,17 +2130,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 135، 120</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2497,22 +2497,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2683,22 +2683,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2750,17 +2750,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401</t>
+          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2812,17 +2812,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 331,882,138، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2931,22 +2931,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2993,22 +2993,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 331,882,138، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3427,22 +3427,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3742,17 +3742,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3985,22 +3985,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>مبالغ: 71,218,857,178، 372,426,828، 368,757,931</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4047,22 +4047,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>مبالغ: 50,484,843,715، 8,849,447,678، 184,887,445</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>مبالغ: 372,426,828، 368,757,931، 335,184,145 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6470,17 +6470,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6718,17 +6718,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>مبالغ: 450,000، 1,000</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>مبالغ: 450,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7276,17 +7276,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 372,426,828، 120</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,12 +577,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4431025114؛ 4530241622</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4431025114؛ 4530241622</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -862,12 +862,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4630548401</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4530828230</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1004,12 +1004,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1044,12 +1044,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>عقد / اتفاقية</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4530828230</t>
+          <t>4530241622</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1124,30 +1124,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4530241622</t>
+          <t>4630548401</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,30 +1164,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>عقد / اتفاقية</t>
+          <t>حكم / صك</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4530241622</t>
-        </is>
-      </c>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1204,7 +1200,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1213,21 +1209,17 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>4630548401</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1244,7 +1236,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1257,7 +1249,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1280,12 +1272,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>حكم / صك</t>
+          <t>مذكرة قضائية</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1293,13 +1285,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4530241622</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1316,7 +1312,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1329,13 +1325,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1352,12 +1348,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>مذكرة قضائية</t>
+          <t>شكوى</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1365,7 +1361,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)</t>
+          <t>عدنان زيني؛ أسامة زيني؛ أحمد زيني (المورّث)؛ عاتقة الحرازي</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1375,7 +1371,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1392,7 +1388,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1415,7 +1411,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1432,7 +1428,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1696,12 +1692,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,12 +1754,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114، 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1820,17 +1816,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>مذكرة طلب النقض على الحكم النهائي</t>
+          <t>-05-11~1.DOC.docx</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1882,12 +1878,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-05-11~1.DOC.docx</t>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1949,7 +1945,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة</t>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2011,7 +2007,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+          <t>ملف مؤقت tmp</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2068,17 +2064,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ملف مؤقت tmp</t>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2130,17 +2126,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2192,17 +2188,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 170، 120</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2254,12 +2250,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 135، 120</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2316,17 +2312,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 135، 120</t>
+          <t>صكوك: 4530828230 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2373,22 +2369,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2435,22 +2431,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>صكوك: 4530828230 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>التماس ضد الحكم ـ نسخة أولى</t>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2507,7 +2503,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+          <t>صورة التقديم (pdf)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2559,22 +2555,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>تفاصيل التقديم ـ موقع توارد</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2621,22 +2617,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>صورة التقديم (pdf)</t>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2688,17 +2684,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401</t>
+          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2750,12 +2746,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 331,882,138، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2807,22 +2803,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2874,17 +2870,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 331,882,138، 120 | قضايا: 42824717</t>
+          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>د. مرفقات المدعي بموقع ناجز (3 ملفات)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2936,17 +2932,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 120,000,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2998,17 +2994,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3060,12 +3056,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3122,12 +3118,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3184,12 +3180,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3241,17 +3237,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3303,22 +3299,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 367,757,931، 331,882,138 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3375,7 +3371,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
+          <t>شكوى لوزير العدل 13-11-1445</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3432,12 +3428,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3494,17 +3490,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3556,12 +3552,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3623,12 +3619,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3680,12 +3676,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3742,17 +3738,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة</t>
+          <t>الشكوى ومرفقاتها</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>م. الشكوى الرابعة لوزير العدل ـ 09-06-1446 (ملفان)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3804,12 +3800,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3866,12 +3862,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450، 120 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>مرفقات الشكوى</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3923,22 +3919,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>مبالغ: 71,218,857,178، 372,426,828، 368,757,931</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>مرفقات الشكوى</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3990,12 +3986,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>مبالغ: 71,218,857,178، 372,426,828، 368,757,931</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -1476,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 5,000,000، 500,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 170، 120</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 450,000، 170</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
+          <t>مبالغ: 478,757,110، 368,757,931، 11,574,017 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 331,882,138، 120 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 331,882,138، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>مبالغ: 478,757,110، 11,574,017، 450,000 | قضايا: 42824717</t>
+          <t>مبالغ: 478,757,110، 368,757,931، 11,574,017 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 500,000، 450,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 450,000، 50,000، 1,000 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 100,000,000، 500,000، 450,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 150,000، 17,000، 450 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 79,929,906، 36,877,936، 150,000 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 137,631,929، 79,924,901 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | مبالغ: 368,757,931، 331,882,138، 137,631,929 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>مبالغ: 11,679,151، 737,500</t>
+          <t>مبالغ: 1,037,259,019، 172,613,467، 14,282,008</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>مبالغ: 120</t>
+          <t>مبالغ: 1,000,070</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>مبالغ: 4,690,483، 2,463,761</t>
+          <t>مبالغ: 120</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>مبالغ: 20,000، 17,000، 1,000</t>
+          <t>مبالغ: 4,690,483، 2,463,761</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>المسحوبات 1434 (zip)</t>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ح-1. المسحوبات (8 ملفات)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>مبالغ: 36,171، 30,000، 3,325</t>
+          <t>مبالغ: 20,000، 17,000، 1,000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>المسحوبات 1435 (zip)</t>
+          <t>المسحوبات 1434 (zip)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5407,17 +5407,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>مبالغ: 60,900، 60,000، 30,000</t>
+          <t>مبالغ: 36,171، 30,000، 25,000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>المسحوبات 1436 (zip)</t>
+          <t>المسحوبات 1435 (zip)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
+          <t>مبالغ: 60,900، 60,000، 30,000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>المسحوبات 2015 (zip)</t>
+          <t>المسحوبات 1436 (zip)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>مبالغ: 100,000,000، 1,000</t>
+          <t>مبالغ: 40,901,050، 1,662,326، 1,390,810</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>المسحوبات 2015 (zip)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-1. المسحوبات (8 ملفات)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>مبالغ: 100,000,000، 46,000، 1,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 450,000، 1,000</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5779,22 +5779,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>دليل/مستند</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5903,22 +5903,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>تفاصيل الشكوى</t>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5965,22 +5965,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 10,851</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>تفاصيل شكوى المجلس الأعلى</t>
+          <t>مزرعة الوادي 1433 (zip)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6027,22 +6027,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 9,290، 9,240</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ح-2. المزرعة (7 ملفات)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>دليل/مستند</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 19,000,500، 35,000، 1,318</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد.docx</t>
+          <t>فلة الوادي 1433 (rar)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
+          <t>تفاصيل الشكوى</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6213,22 +6213,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>إحالة قضائية</t>
+          <t>واقعة</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6280,17 +6280,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>صكوك: 4630548401 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6342,17 +6342,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>مبالغ: 135 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>واقعة</t>
+          <t>إحالة قضائية</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6528,17 +6528,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>صكوك: 4630548401 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6590,17 +6590,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>مبالغ: 135 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6652,17 +6652,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>مبالغ: 368,757,931، 97,762,042، 27,932,012 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6776,17 +6776,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6838,17 +6838,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6900,17 +6900,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>مبالغ: 500,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7024,17 +7024,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>مبالغ: 450,000، 1,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>أ. المجلد الرئيسي للقضية (39 ملفاً)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 500,000، 1,000</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>مبالغ: 372,426,828، 120</t>
+          <t>مبالغ: 500,000، 450,000، 1,000</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7334,17 +7334,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>مبالغ: 331,882,138، 120,000,000، 110,672,379</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7520,17 +7520,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 372,426,828، 120</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>أمر تنفيذ عدنان ـ نسخة</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7582,17 +7582,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>مبالغ: 331,882,138، 120,000,000، 110,672,379</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>ج. محاضر ضبط الجلسات (16 ملفاً)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7644,17 +7644,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>صكوك: 4530241622 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
+          <t>و. مستندات طلب الالتماس (5 ملفات)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7706,17 +7706,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>صكوك: 4431025114 | قضايا: 42824717</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7830,17 +7830,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>مبالغ: 556,415</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -7892,17 +7892,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4530241622 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ي. مرفقات خطاب شكوى وزير العدل الأولى والثانية (21 ملفاً)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7954,17 +7954,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>صكوك: 4431025114 | قضايا: 42824717</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 3,000,000</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>محضر اجتماع تقسيم شركات ابار وزيني و شيكات الامير احمد و بيان شيكات القروض البنكية.pdf</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8140,17 +8140,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 556,415</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>موجز إعادة فتح الشكوى</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>صورة التقديم (jpg)</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+          <t>صورة تقديم الشكوى</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8455,45 +8455,355 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>A113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>A114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>A115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>A116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>A117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>واقعة</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>قضايا: 42824717</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>يحتاج مراجعة</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
+++ b/zaini_case_audit_output/outputs/excel/07_central_and_new_outputs.xlsx
@@ -1476,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>مبالغ: 19,000,500، 35,000، 1,318</t>
+          <t>مبالغ: 19,000,500</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>مبالغ: 3,000,000</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>محضر اجتماع تقسيم شركات ابار وزيني و شيكات الامير احمد و بيان شيكات القروض البنكية.pdf</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8078,17 +8078,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>قضايا: 42824717</t>
+          <t>مبالغ: 556,415</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ح-3. فلة الوادي (5 ملفات)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8140,17 +8140,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>مبالغ: 556,415</t>
+          <t>قضايا: 42824717</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ح-3. فلة الوادي (5 ملفات)</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>أ. المجلد الرئيسي للقضية</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8331,12 +8331,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+          <t>صورة تقديم الشكوى</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>أ. المجلد الرئيسي للقضية</t>
+          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى</t>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ط. الشكوى الأولى لوزير العدل رقم 230747621 ـ 30-04-1445 (4 ملفات)</t>
+          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+          <t>موجز إعادة فتح الشكوى</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>موجز إعادة فتح الشكوى</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ك. إعادة فتح الشكوى الثانية 199058 ـ 13-11-1445 (7 ملفات)</t>
+          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
+          <t>صورة التقديم (jpg)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>صورة التقديم (jpg)</t>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ن. شكوى أسامة زيني إلى ولي العهد ـ 17-11-1445 (9 ملفات)</t>
+          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+          <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ب. المذكرات المقدمة من الطرفين (49 ملفاً)</t>
+          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8742,68 +8742,6 @@
         </is>
       </c>
       <c r="L117" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>A117</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>واقعة</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>قضايا: 42824717</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>صفحة 1 من تقديم الشكوى</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>ل. الشكوى الثالثة لوزير العدل ـ 26-04-1446 (7 ملفات)</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>ظهر آلياً عبر مطابقة أرقام/مبالغ في النص</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>يحتاج مراجعة</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>يحتمل أن يكون ذا صلة بالدراسة - يتطلب تحققاً قانونياً</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>عرض على المحامي للمطابقة مع فهرس الدراسة</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>
